--- a/artfynd/A 4287-2024 artfynd.xlsx
+++ b/artfynd/A 4287-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129523684</v>
       </c>
       <c r="B2" t="n">
-        <v>58157</v>
+        <v>58160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129523823</v>
       </c>
       <c r="B3" t="n">
-        <v>58265</v>
+        <v>58268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4287-2024 artfynd.xlsx
+++ b/artfynd/A 4287-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129523684</v>
       </c>
       <c r="B2" t="n">
-        <v>58160</v>
+        <v>58165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129523823</v>
       </c>
       <c r="B3" t="n">
-        <v>58268</v>
+        <v>58273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4287-2024 artfynd.xlsx
+++ b/artfynd/A 4287-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129523684</v>
       </c>
       <c r="B2" t="n">
-        <v>58165</v>
+        <v>58166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129523823</v>
       </c>
       <c r="B3" t="n">
-        <v>58273</v>
+        <v>58274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4287-2024 artfynd.xlsx
+++ b/artfynd/A 4287-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129523684</v>
+        <v>129523823</v>
       </c>
       <c r="B2" t="n">
-        <v>58166</v>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607225</v>
+        <v>607247</v>
       </c>
       <c r="R2" t="n">
-        <v>6727792</v>
+        <v>6727775</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -785,32 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129523823</v>
+        <v>129523684</v>
       </c>
       <c r="B3" t="n">
-        <v>58274</v>
+        <v>58388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607247</v>
+        <v>607225</v>
       </c>
       <c r="R3" t="n">
-        <v>6727775</v>
+        <v>6727792</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,12 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,222 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan fågelinventeringar C240036</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129523822</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>607274</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6727850</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Petter Andersson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan fågelinventeringar C240036</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129523815</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bergslagsbanan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>607217</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6727735</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>

--- a/artfynd/A 4287-2024 artfynd.xlsx
+++ b/artfynd/A 4287-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523823</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523684</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523822</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,8 +1124,19 @@
           <t>Bergslagsbanan fågelinventeringar C240036</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129523815</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>